--- a/data/P2/P2T2_BQ3.xlsx
+++ b/data/P2/P2T2_BQ3.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0165097F-5A2C-3F4A-A209-944DEA346970}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A33C199-41CC-B744-AF96-3C52C867A185}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="32600" yWindow="3540" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -217,13 +218,63 @@
   </si>
   <si>
     <t>困難的</t>
+  </si>
+  <si>
+    <t>Today, communication and travel are fast. But a long time ago, things were very different.</t>
+  </si>
+  <si>
+    <t>現在，通訊和旅行都很快速。但很久以前，情況非常不同。</t>
+  </si>
+  <si>
+    <t>Long ago, people used letters to communicate. They mailed letters to each other.</t>
+  </si>
+  <si>
+    <t>很久以前，人們用信件來溝通。他們互相寄信。</t>
+  </si>
+  <si>
+    <t>Letters were carried by horse and cart, and later by train or boat.</t>
+  </si>
+  <si>
+    <t>信件靠馬車運送，後來則靠火車或船隻。</t>
+  </si>
+  <si>
+    <t>Now people use e-mail, text messages, or phone calls to communicate quickly.</t>
+  </si>
+  <si>
+    <t>現在人們使用電子郵件、簡訊或電話來快速溝通。</t>
+  </si>
+  <si>
+    <t>Airplanes long ago were slow and didn't fly very far.</t>
+  </si>
+  <si>
+    <t>很久以前的飛機速度很慢，也飛不遠。</t>
+  </si>
+  <si>
+    <t>Airplanes are now high-speed and can fly to places far away.</t>
+  </si>
+  <si>
+    <t>現在的飛機是高速的，可以飛到很遠的地方。</t>
+  </si>
+  <si>
+    <t>They carry people, letters, food and other things to different places around the world.</t>
+  </si>
+  <si>
+    <t>它們載著人、信件、食物和其他物品到世界各地不同的地方。</t>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -244,6 +295,15 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -268,11 +328,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -937,4 +1000,82 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172B9B67-863D-8F42-89D5-E2DB797B9BE2}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P2/P2T2_BQ3.xlsx
+++ b/data/P2/P2T2_BQ3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A33C199-41CC-B744-AF96-3C52C867A185}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C4E0A5-D928-3F42-AA49-10B0A71A92B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32600" yWindow="3540" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="32600" yWindow="3540" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -267,6 +267,188 @@
   </si>
   <si>
     <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dɪˈlɪvə(r)/</t>
+  </si>
+  <si>
+    <t>de-li-ver</t>
+  </si>
+  <si>
+    <t>/ˈreɪdiəʊ/</t>
+  </si>
+  <si>
+    <t>ra-di-o</t>
+  </si>
+  <si>
+    <t>/ˈɪntənet/</t>
+  </si>
+  <si>
+    <t>In-ter-net</t>
+  </si>
+  <si>
+    <t>/ˌɪnfəˈmeɪʃn/</t>
+  </si>
+  <si>
+    <t>in-for-ma-tion</t>
+  </si>
+  <si>
+    <t>/ˈferi/</t>
+  </si>
+  <si>
+    <t>fer-ry</t>
+  </si>
+  <si>
+    <t>/ˌsʌbməˈriːn/</t>
+  </si>
+  <si>
+    <t>sub-ma-rine</t>
+  </si>
+  <si>
+    <t>/ˈməʊtəsaɪkl/</t>
+  </si>
+  <si>
+    <t>mo-tor-cy-cle</t>
+  </si>
+  <si>
+    <t>/ˈkæmpə(r)/</t>
+  </si>
+  <si>
+    <t>cam-per</t>
+  </si>
+  <si>
+    <t>/trʌk/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˌdʌbl ˈdekə(r)/</t>
+  </si>
+  <si>
+    <t>dou-ble-deck-er</t>
+  </si>
+  <si>
+    <t>/ˈkeɪbl kɑː(r)/</t>
+  </si>
+  <si>
+    <t>ca-ble car</t>
+  </si>
+  <si>
+    <t>/ˈsʌbweɪ/</t>
+  </si>
+  <si>
+    <t>sub-way</t>
+  </si>
+  <si>
+    <t>/laɪt ˈræpɪd ˈtrænzɪt/</t>
+  </si>
+  <si>
+    <t>Light Ra-pid Tran-sit</t>
+  </si>
+  <si>
+    <t>/ˈplætfɔːm/</t>
+  </si>
+  <si>
+    <t>plat-form</t>
+  </si>
+  <si>
+    <t>/ˈhelɪkɒptə(r)/</t>
+  </si>
+  <si>
+    <t>hel-i-cop-ter</t>
+  </si>
+  <si>
+    <t>/ˈeəpleɪn/</t>
+  </si>
+  <si>
+    <t>air-plane</t>
+  </si>
+  <si>
+    <t>/flaɪt/</t>
+  </si>
+  <si>
+    <t>/ˈpæsɪndʒə(r)/</t>
+  </si>
+  <si>
+    <t>pas-sen-ger</t>
+  </si>
+  <si>
+    <t>/ˈtɜːmɪnl/</t>
+  </si>
+  <si>
+    <t>ter-mi-nal</t>
+  </si>
+  <si>
+    <t>/tʃek ɪn/</t>
+  </si>
+  <si>
+    <t>/ˈpɑːspɔːt/</t>
+  </si>
+  <si>
+    <t>pass-port</t>
+  </si>
+  <si>
+    <t>/ˈtɪkɪt/</t>
+  </si>
+  <si>
+    <t>tick-et</t>
+  </si>
+  <si>
+    <t>/ˈlʌɡɪdʒ/</t>
+  </si>
+  <si>
+    <t>lug-gage</t>
+  </si>
+  <si>
+    <t>/dɪˈleɪd/</t>
+  </si>
+  <si>
+    <t>de-layed</t>
+  </si>
+  <si>
+    <t>/əˈraɪv/</t>
+  </si>
+  <si>
+    <t>ar-rive</t>
+  </si>
+  <si>
+    <t>/ˈentə(r)/</t>
+  </si>
+  <si>
+    <t>en-ter</t>
+  </si>
+  <si>
+    <t>/ˈvɪzɪt/</t>
+  </si>
+  <si>
+    <t>vis-it</t>
+  </si>
+  <si>
+    <t>/ˈkraʊdɪd/</t>
+  </si>
+  <si>
+    <t>crowd-ed</t>
+  </si>
+  <si>
+    <t>/ˌnɪəˈbaɪ/</t>
+  </si>
+  <si>
+    <t>near-by</t>
+  </si>
+  <si>
+    <t>/ˈdɪfɪkəlt/</t>
+  </si>
+  <si>
+    <t>diffi-cult</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -652,10 +834,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,8 +852,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -676,8 +872,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -687,8 +889,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -698,8 +906,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -709,8 +923,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -720,8 +940,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -731,8 +957,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -742,8 +974,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -753,8 +991,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -764,8 +1008,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -775,8 +1025,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -786,8 +1042,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -797,8 +1059,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -808,8 +1076,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -819,8 +1093,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -830,8 +1110,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -841,8 +1127,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -852,8 +1144,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -863,8 +1161,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -874,8 +1178,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -885,8 +1195,14 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -896,8 +1212,14 @@
       <c r="C22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -907,8 +1229,14 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -918,8 +1246,14 @@
       <c r="C24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -929,8 +1263,14 @@
       <c r="C25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -940,8 +1280,14 @@
       <c r="C26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E26" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -951,8 +1297,14 @@
       <c r="C27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -962,8 +1314,14 @@
       <c r="C28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>129</v>
+      </c>
+      <c r="E28" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -973,8 +1331,14 @@
       <c r="C29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -984,8 +1348,14 @@
       <c r="C30">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -994,6 +1364,12 @@
       </c>
       <c r="C31">
         <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/data/P2/P2T2_BQ3.xlsx
+++ b/data/P2/P2T2_BQ3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64C4E0A5-D928-3F42-AA49-10B0A71A92B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310AA740-132F-0443-93F9-49B2AE815CA7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32600" yWindow="3540" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="28300" yWindow="2460" windowWidth="28060" windowHeight="17660" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="170">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -450,6 +450,100 @@
   <si>
     <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Take things or letters to people’s places</t>
+  </si>
+  <si>
+    <t>A machine that plays sound and news</t>
+  </si>
+  <si>
+    <t>A web on computers to get news and pictures</t>
+  </si>
+  <si>
+    <t>News, facts or messages you learn</t>
+  </si>
+  <si>
+    <t>A big boat that carries cars and people across water</t>
+  </si>
+  <si>
+    <t>A boat that can travel under the sea</t>
+  </si>
+  <si>
+    <t>A fast two-wheeled vehicle with an engine</t>
+  </si>
+  <si>
+    <t>A car or van with beds for sleeping on trips</t>
+  </si>
+  <si>
+    <t>A big vehicle to carry heavy goods</t>
+  </si>
+  <si>
+    <t>A bus with two floors for passengers</t>
+  </si>
+  <si>
+    <t>A hanging car moving along wires on hills</t>
+  </si>
+  <si>
+    <t>A train running under the city ground</t>
+  </si>
+  <si>
+    <t>A light train running on tracks above streets</t>
+  </si>
+  <si>
+    <t>The flat place where people wait for trains</t>
+  </si>
+  <si>
+    <t>A flying machine with big spinning top blades</t>
+  </si>
+  <si>
+    <t>A big flying vehicle that carries people far away</t>
+  </si>
+  <si>
+    <t>One trip taken by plane</t>
+  </si>
+  <si>
+    <t>A person who rides on buses, trains or planes</t>
+  </si>
+  <si>
+    <t>A big building where people get on planes or ships</t>
+  </si>
+  <si>
+    <t>Show your ticket before you take a plane</t>
+  </si>
+  <si>
+    <t>A small book to show who you are for trips to other countries</t>
+  </si>
+  <si>
+    <t>A small paper card to let you ride vehicles</t>
+  </si>
+  <si>
+    <t>Bags and boxes you carry on trips</t>
+  </si>
+  <si>
+    <t>The bus or plane leaves later than planned</t>
+  </si>
+  <si>
+    <t>Reach the place you want to go</t>
+  </si>
+  <si>
+    <t>Walk into a room, station or plane</t>
+  </si>
+  <si>
+    <t>Go to see a place or person</t>
+  </si>
+  <si>
+    <t>Full of many people with little space</t>
+  </si>
+  <si>
+    <t>Not far away, close to you</t>
+  </si>
+  <si>
+    <t>Not easy to do or understand</t>
   </si>
 </sst>
 </file>
@@ -834,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -842,7 +936,7 @@
     <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -858,11 +952,14 @@
       <c r="E1" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -878,8 +975,11 @@
       <c r="E2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -895,8 +995,11 @@
       <c r="E3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="F3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,8 +1015,11 @@
       <c r="E4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -929,8 +1035,11 @@
       <c r="E5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +1055,11 @@
       <c r="E6" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,8 +1075,11 @@
       <c r="E7" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -980,8 +1095,11 @@
       <c r="E8" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -997,8 +1115,11 @@
       <c r="E9" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1014,8 +1135,11 @@
       <c r="E10" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1031,8 +1155,11 @@
       <c r="E11" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1048,8 +1175,11 @@
       <c r="E12" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1065,8 +1195,11 @@
       <c r="E13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1082,8 +1215,11 @@
       <c r="E14" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1099,8 +1235,11 @@
       <c r="E15" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1116,8 +1255,11 @@
       <c r="E16" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -1133,8 +1275,11 @@
       <c r="E17" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1150,8 +1295,11 @@
       <c r="E18" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1167,8 +1315,11 @@
       <c r="E19" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1184,8 +1335,11 @@
       <c r="E20" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1201,8 +1355,11 @@
       <c r="E21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1218,8 +1375,11 @@
       <c r="E22" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1235,8 +1395,11 @@
       <c r="E23" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1252,8 +1415,11 @@
       <c r="E24" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -1269,8 +1435,11 @@
       <c r="E25" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1286,8 +1455,11 @@
       <c r="E26" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1303,8 +1475,11 @@
       <c r="E27" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1320,8 +1495,11 @@
       <c r="E28" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1337,8 +1515,11 @@
       <c r="E29" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -1354,8 +1535,11 @@
       <c r="E30" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1370,6 +1554,9 @@
       </c>
       <c r="E31" t="s">
         <v>136</v>
+      </c>
+      <c r="F31" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
